--- a/output/pdf_financials_xlsx/BCC.H.xlsx
+++ b/output/pdf_financials_xlsx/BCC.H.xlsx
@@ -527,50 +527,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -579,55 +561,35 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -641,50 +603,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -693,55 +637,35 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -750,55 +674,35 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -807,55 +711,35 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -864,55 +748,35 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.047161</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.04733</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.048668</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.044812</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.045042</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.045452</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.045771</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.044933</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.044789</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.04523</v>
       </c>
     </row>
     <row r="11">
@@ -926,50 +790,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="3" t="n">
+        <v>-0.04733</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-0.048668</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.044812</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-0.045042</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-0.045452</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>-0.045771</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>-0.044933</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>-0.044789</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>-0.04523</v>
       </c>
     </row>
     <row r="12">
@@ -978,55 +824,35 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1035,55 +861,35 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -1092,55 +898,35 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1149,55 +935,35 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1211,50 +977,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>-0.038465</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.036297</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-0.037383</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-0.040539</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-0.042009</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>-0.040512</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>-0.039176</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>-0.038375</v>
       </c>
     </row>
     <row r="17">
@@ -1263,55 +1011,35 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1439,50 +1167,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="3" t="n">
+        <v>-0.038465</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.036297</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-0.037383</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-0.040539</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>-0.042009</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>-0.040512</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>-0.039176</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>-0.038375</v>
       </c>
     </row>
     <row r="21">
@@ -1491,55 +1201,35 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1548,55 +1238,35 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1610,50 +1280,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v>-0.038465</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.036297</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-0.037383</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-0.040539</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>-0.042009</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>-0.040512</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>-0.039176</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>-0.038375</v>
       </c>
     </row>
     <row r="24">
@@ -1667,50 +1319,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>-0.005</v>
       </c>
     </row>
     <row r="25">
@@ -1724,50 +1358,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>-0.005</v>
       </c>
     </row>
     <row r="26">
@@ -1838,50 +1454,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v>-0.038465</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.036297</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-0.037383</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-0.040539</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>-0.042009</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>-0.040512</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>-0.039176</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>-0.038375</v>
       </c>
     </row>
     <row r="28">
@@ -1890,55 +1488,35 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1952,50 +1530,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C29" s="3" t="n">
+        <v>-0.038465</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.036297</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-0.037383</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-0.040539</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>-0.042009</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>-0.040512</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>-0.039176</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>-0.038375</v>
       </c>
     </row>
     <row r="30">
@@ -2066,50 +1626,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5104,50 +4646,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-0.038465</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.036297</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-0.037383</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>-0.040539</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>-0.042009</v>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v>-0.040512</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>-0.039176</v>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>-0.038375</v>
       </c>
     </row>
     <row r="100">
@@ -5156,55 +4680,35 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5213,55 +4717,35 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -5270,55 +4754,35 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -5327,55 +4791,35 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>-0.001174</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0.001038</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.001819</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>-0.001422</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0.000312</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>-0.000305</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>0.002697</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>-0.000773</v>
+      </c>
+      <c r="K103" s="3" t="n">
+        <v>0.000947</v>
       </c>
     </row>
     <row r="104">
@@ -5384,55 +4828,35 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.000995</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>-0.001248</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>-0.000461</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.000274</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>-2.6e-05</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0.001374</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>0.001159</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>0.001095</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>-0.00081</v>
+      </c>
+      <c r="K104" s="3" t="n">
+        <v>0.000463</v>
       </c>
     </row>
     <row r="105">
@@ -5441,55 +4865,35 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -5498,55 +4902,35 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.000995</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.002422</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.000577</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.002093</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>-0.001448</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0.001686</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>0.000854</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>0.003792</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>-0.001583</v>
+      </c>
+      <c r="K106" s="3" t="n">
+        <v>0.00141</v>
       </c>
     </row>
     <row r="107">
@@ -5555,55 +4939,35 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -5612,55 +4976,35 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -5669,55 +5013,35 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -5726,55 +5050,35 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -5783,55 +5087,35 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -5840,55 +5124,35 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5897,55 +5161,35 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -5954,55 +5198,35 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -6011,55 +5235,35 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -6068,55 +5272,35 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -6125,55 +5309,35 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -6182,55 +5346,35 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -6296,55 +5440,35 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -6353,55 +5477,35 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -6410,55 +5514,35 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -6467,55 +5551,35 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -6524,55 +5588,35 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -6581,55 +5625,35 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -6638,55 +5662,35 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -6752,55 +5756,35 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -6866,55 +5850,35 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.84039</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.802992</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.762105</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0.723002</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>0.684612</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>0.645781</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>0.606928</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>0.564065</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>0.527345</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>0.486586</v>
       </c>
     </row>
     <row r="131">
@@ -6923,55 +5887,35 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -6980,55 +5924,35 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.037398</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.040887</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.039103</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-0.03839</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>-0.038831</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>-0.038853</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>-0.042863</v>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>-0.03672</v>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>-0.040759</v>
+      </c>
+      <c r="K132" s="3" t="n">
+        <v>-0.036965</v>
       </c>
     </row>
     <row r="133">
@@ -7037,55 +5961,35 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.802992</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.762105</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.723002</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0.684612</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>0.645781</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>0.606928</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>0.564065</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>0.527345</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>0.486586</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>0.449621</v>
       </c>
     </row>
     <row r="134">
@@ -7094,55 +5998,35 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -7213,7 +6097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8214,6 +7098,2874 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.038465</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.036297</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>-0.037383</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>-0.040539</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>-0.042009</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>-0.040512</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>-0.039176</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>-0.038375</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Change in non-cash operating working capital</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>- Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-0.001174</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.001038</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-0.001819</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>-0.001422</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0.000312</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>-0.000305</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0.002697</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>-0.000773</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0.000947</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Change in non-cash operating working capital</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>- Accounts payable</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>-2.6e-05</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0.001374</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.001159</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0.001095</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>-0.00081</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0.000463</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Change in non-cash operating working capital</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Change in non-cash operating working capital total</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" s="5" t="n">
+        <v>0.001202</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-0.002422</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.000577</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>-0.002093</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>-0.001448</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0.001686</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.000854</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0.003792</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>-0.001583</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0.00141</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NET CHANGE IN CASH AND CASH</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EQUIVALENTS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-0.040887</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>-0.039103</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>-0.03839</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>-0.038831</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>-0.038853</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>-0.042863</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>-0.03672</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>-0.040759</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>-0.036965</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NET CHANGE IN CASH AND CASH</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CASH AND CASH EQUIVALENTS, beginning of</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.802992</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.762105</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.723002</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0.684612</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>0.645781</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0.606928</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0.564065</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>0.527345</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0.486586</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CASH AND CASH EQUIVALENTS, end of year</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.762105</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.723002</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.684612</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0.645781</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0.606928</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.564065</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>0.527345</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0.486586</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>0.449621</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Investment income</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.008865</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.008987999999999999</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.008515</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>0.007659</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>0.004913</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.003762</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-0.04733</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>-0.048668</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>-0.044812</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>-0.045042</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>-0.045452</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>-0.045771</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Change in non-cash operating working capital</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>- Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-0.001248</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-0.000461</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>-0.000274</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>-2.6e-05</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FOR THE YEARS ENDED JUNE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Investment income 8,865</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" s="5" t="n">
+        <v>0.008560999999999999</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Operating expenses -47,330</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" s="5" t="n">
+        <v>-0.047161</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Net loss -38,465</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" s="5" t="n">
+        <v>-0.0386</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Change in non-cash operating working capital</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>- Prepaid expenses -1,174</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" s="5" t="n">
+        <v>0.000207</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Change in non-cash operating working capital</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>- Accounts payable and accrued liabilities -1,248</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0.000995</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NET CHANGE IN CASH AND CASH</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EQUIVALENTS -40,887</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" s="5" t="n">
+        <v>-0.037398</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NET CHANGE IN CASH AND CASH</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CASH AND CASH EQUIVALENTS, beginning of 802,992</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.84039</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CASH AND CASH EQUIVALENTS, end of year 762,105</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.802992</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>INCOME</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Investment income</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.008865</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.008987999999999999</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0.008515</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0.007659</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0.004913</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0.003762</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0.004421</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0.005613</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0.006855</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Audit, legal, regulatory and other fees</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>-0.028146</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>-0.029178</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>-0.02666</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>-0.026137</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>-0.025942</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>-0.026894</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>-0.026939</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>-0.02711</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>-0.027399</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Insurance, and office supplies</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>-0.007603</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-0.006906</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>-0.006557</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>-0.006892</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>-0.00744</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>-0.006938</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>-0.006054</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>-0.005697</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>-0.006021</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Management compensation (Note 8)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>-0.009299999999999999</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.01065</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>-0.009549999999999999</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>-0.002281</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>-0.001934</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>-0.002045</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>-0.002213</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>-0.00207</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>-0.001939</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>-0.00194</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>-0.001982</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>-0.00181</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.047161</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.04733</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.048668</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.044812</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0.045042</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>0.045452</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.045771</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0.044933</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>0.044789</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>0.04523</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>-0.037383</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>-0.040539</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>-0.042009</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>-0.040512</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>-0.039176</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>-0.038375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Income taxes (Note 6)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NET LOSS AND COMPREHENSIVE LOSS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>-0.036297</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>-0.037383</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>-0.040539</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>-0.042009</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>-0.040512</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>-0.039176</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>-0.038375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LOSS PER SHARE, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>-4e-09</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>-4e-09</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>8.3895</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>8.3895</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>8.3895</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>8.3895</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>8.3895</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>8.3895</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>8.3895</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>8.3895</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>8.3895</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Loss before items below</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>-0.038465</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>-0.036297</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>-0.037383</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NET LOSS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>-0.038465</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OTHER COMPREHENSIVE INCOME</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>COMPREHENSIVE LOSS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>-0.038465</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FOR THE YEARS ENDED JUNE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>INCOME</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Investment income 8,865</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" s="5" t="n">
+        <v>0.008560999999999999</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Audit, legal, regulatory and other fees -28,146</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" s="5" t="n">
+        <v>-0.02894</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Insurance, and office supplies -7,603</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" s="5" t="n">
+        <v>-0.00612</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Management compensation (Note 8) -9,300</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" s="5" t="n">
+        <v>-0.0094</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Other -2,281</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" s="5" t="n">
+        <v>-0.002701</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Loss before items below -38,465</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" s="5" t="n">
+        <v>-0.0386</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Income taxes (Note 6) -</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>NET LOSS -38,465</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" s="5" t="n">
+        <v>-0.0386</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OTHER COMPREHENSIVE INCOME -</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>COMPREHENSIVE LOSS -38,465</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" s="5" t="n">
+        <v>-0.0386</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LOSS PER SHARE, basic and diluted -0.005</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Basic and diluted 8,389,500</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>8.3895</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
